--- a/estructurasDatosMemoria (2).xlsx
+++ b/estructurasDatosMemoria (2).xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="EstructuraDatos" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="EstructuraDatos" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
   <si>
     <t xml:space="preserve">Ejemplo de cómo representar las estructuras de datos según lo visto en teoría:</t>
   </si>
@@ -79,13 +79,43 @@
     <t xml:space="preserve">$coleccionJuegos =</t>
   </si>
   <si>
-    <t xml:space="preserve">…</t>
+    <t xml:space="preserve">Max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trevor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingrid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zangief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daven</t>
   </si>
   <si>
     <t xml:space="preserve">Tipo: Indexado multidimensional</t>
   </si>
   <si>
-    <t xml:space="preserve">Tipos de datos: .... Clave … . Valores ... y …</t>
+    <t xml:space="preserve">Tipos de datos: String y enteros. Clave . Valores ... y …</t>
   </si>
   <si>
     <t xml:space="preserve">Guarda información de …</t>
@@ -98,7 +128,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -174,6 +204,12 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -253,72 +289,84 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -394,188 +442,419 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18A303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369A3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A33E03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8E03A3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="C99C00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="C9211E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000EE"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551A8B"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
-  <sheetFormatPr defaultColWidth="10.70703125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K28"/>
+  <sheetFormatPr defaultColWidth="10.70703125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="1" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="4"/>
+      <c r="G3" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="7" t="s">
+      <c r="E4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="0" t="s">
+      <c r="H7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="8" t="n">
+      <c r="B16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="E16" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="G17" s="0" t="s">
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="C19" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="E20" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="12"/>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="12"/>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="12"/>
-      <c r="G21" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="H21" s="0" t="s">
-        <v>19</v>
+      <c r="K21" s="11" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="12"/>
+      <c r="A22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="16" t="s">
-        <v>20</v>
+      <c r="B25" s="18" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="16" t="s">
-        <v>21</v>
+      <c r="B26" s="18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="16" t="s">
-        <v>22</v>
+      <c r="A27" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="18"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
